--- a/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Apuntes.xlsx
+++ b/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Apuntes.xlsx
@@ -5,25 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAW\asignaturas\BI\EXCEL\Evaluacion2\noviembre\Martes 26 noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAW\asignaturas\BI\EXCEL\Evaluacion2\noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6A002D-824D-420E-962E-71BBA891B3B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB75D64E-0FBC-47E7-B7CD-05AA81F6FD27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12090" activeTab="3" xr2:uid="{C1A1F3CA-DEB3-4116-98D3-6D6318BE211A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12090" activeTab="5" xr2:uid="{C1A1F3CA-DEB3-4116-98D3-6D6318BE211A}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="2" r:id="rId1"/>
     <sheet name="buscarV" sheetId="1" r:id="rId2"/>
     <sheet name="ejercicio 1" sheetId="5" r:id="rId3"/>
     <sheet name="gráficos" sheetId="6" r:id="rId4"/>
+    <sheet name="BuscarX" sheetId="7" r:id="rId5"/>
+    <sheet name="Fechas" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlcn.WorksheetConnection_gráficosC7F101" hidden="1">gráficos!$C$7:$F$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="23" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>1) ejemplo 1</t>
   </si>
@@ -224,20 +226,72 @@
   <si>
     <t>Suma de abril</t>
   </si>
+  <si>
+    <t>Lunes</t>
+  </si>
+  <si>
+    <t>Martes</t>
+  </si>
+  <si>
+    <t>Miércoles</t>
+  </si>
+  <si>
+    <t>Jueves</t>
+  </si>
+  <si>
+    <t>Viernes</t>
+  </si>
+  <si>
+    <t>Sábado</t>
+  </si>
+  <si>
+    <t>Domingo</t>
+  </si>
+  <si>
+    <t>diciembre - 2000</t>
+  </si>
+  <si>
+    <t>Número de días</t>
+  </si>
+  <si>
+    <t>Fecha Inicial</t>
+  </si>
+  <si>
+    <t>Festivos</t>
+  </si>
+  <si>
+    <t>Hora de entrada</t>
+  </si>
+  <si>
+    <t>Dia Lab Ant</t>
+  </si>
+  <si>
+    <t>Fecha Final</t>
+  </si>
+  <si>
+    <t>fecha de referencia:</t>
+  </si>
+  <si>
+    <t>X meses después:</t>
+  </si>
+  <si>
+    <t>X meses antes:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;;[Red]#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Franklin Gothic Book"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -245,12 +299,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Franklin Gothic Book"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,6 +354,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -306,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -344,9 +435,6 @@
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -354,6 +442,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1465,6 +1586,27 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF">
+                  <a:alpha val="90000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="E28394"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:srgbClr val="E28394">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
             <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
@@ -1949,6 +2091,27 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF">
+                  <a:alpha val="90000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="77A2BB"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:srgbClr val="77A2BB">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
             <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
@@ -2433,6 +2596,27 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF">
+                  <a:alpha val="90000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="8DAB8E"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:srgbClr val="8DAB8E">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
             <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
@@ -3096,7 +3280,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[buscarv.xlsx]gráficos!TablaDinámica4</c:name>
+    <c:name>[Apuntes.xlsx]gráficos!TablaDinámica4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3126,17 +3310,88 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
               <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent6"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent6"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent6"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent6"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent6"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
         </c:marker>
       </c:pivotFmt>
     </c:pivotFmts>
@@ -6381,6 +6636,218 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>815578</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>89297</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>796527</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>51196</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectángulo 12">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00FA69C2-499E-49A8-995B-EB2072175648}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7733109" y="1910953"/>
+          <a:ext cx="1957387" cy="366712"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4 DE DICIEMBRE</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>184547</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>172639</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>513159</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>134539</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectángulo 13">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C2AE674-D080-425E-BD21-C4E3AFAF5249}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8090297" y="2399108"/>
+          <a:ext cx="1316831" cy="366712"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Buscarx</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>354806</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>295274</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>80963</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectángulo 14">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1373A606-8A91-4573-B678-3378D67E2C8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8260556" y="2952751"/>
+          <a:ext cx="928687" cy="366712"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Fechas</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6533,6 +7000,144 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19707</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>131378</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>249621</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85395</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectángulo 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6643210-52B1-4EE6-93BC-FF46B7523BC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="781707" y="131378"/>
+          <a:ext cx="991914" cy="335017"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100"/>
+            <a:t>Fecha del mes</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7883</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>106416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>118241</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>157655</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectángulo 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7D52B58-94AE-47AF-934E-055E1FE084E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="769883" y="487416"/>
+          <a:ext cx="10003220" cy="241739"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100"/>
+            <a:t>1. La</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100" baseline="0"/>
+            <a:t> funcion FECHA.MES: Funcion entendible. Consiste en la suma o resta de meses a una determinada. ⚠️ No se pueden sumar meses de otra forma más accesible</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="FP" refreshedDate="45628.388513310187" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{477C061B-19F7-4DB1-9ED9-1E87A5200B78}">
   <cacheSource type="external" connectionId="1"/>
@@ -6610,7 +7215,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF192066-03ED-4ACB-997B-4D39A9E47C78}" name="TablaDinámica4" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF192066-03ED-4ACB-997B-4D39A9E47C78}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="H8:K9" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="4">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -6755,22 +7360,22 @@
         <a:srgbClr val="957A99"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Recorte">
+    <a:fontScheme name="Cambria-Calibri">
       <a:majorFont>
-        <a:latin typeface="Franklin Gothic Book" panose="020B0503020102020204"/>
+        <a:latin typeface="Cambria" panose="02040503050406030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="メイリオ"/>
-        <a:font script="Hang" typeface="돋움"/>
-        <a:font script="Hans" typeface="华文楷体"/>
-        <a:font script="Hant" typeface="微軟正黑體"/>
-        <a:font script="Arab" typeface="Tahoma"/>
-        <a:font script="Hebr" typeface="Aharoni"/>
-        <a:font script="Thai" typeface="LilyUPC"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="黑体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
         <a:font script="Knda" typeface="Tunga"/>
         <a:font script="Guru" typeface="Raavi"/>
         <a:font script="Cans" typeface="Euphemia"/>
@@ -6787,21 +7392,21 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Tahoma"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Franklin Gothic Book" panose="020B0503020102020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="メイリオ"/>
-        <a:font script="Hang" typeface="돋움"/>
-        <a:font script="Hans" typeface="华文楷体"/>
-        <a:font script="Hant" typeface="微軟正黑體"/>
-        <a:font script="Arab" typeface="Tahoma"/>
-        <a:font script="Hebr" typeface="Aharoni"/>
-        <a:font script="Thai" typeface="LilyUPC"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -6975,10 +7580,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8DA10F8-0EF7-48EA-90FF-9F055AACE164}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6991,22 +7596,22 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B4:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="5.44140625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="11.5546875" style="2"/>
+    <col min="3" max="3" width="8" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
@@ -7023,7 +7628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>5</v>
       </c>
@@ -7043,7 +7648,7 @@
         <v>ESP</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
@@ -7062,14 +7667,14 @@
         <f t="shared" ref="F9:F15" si="1">VLOOKUP(C9,H$10:K$13,4,FALSE)</f>
         <v>EN</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>8</v>
       </c>
@@ -7101,7 +7706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>5</v>
       </c>
@@ -7133,7 +7738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -7165,7 +7770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>10</v>
       </c>
@@ -7197,7 +7802,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
@@ -7217,7 +7822,7 @@
         <v>CH</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
         <v>12</v>
       </c>
@@ -7252,24 +7857,24 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="B4:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" style="2" customWidth="1"/>
-    <col min="7" max="10" width="11.5546875" style="2"/>
-    <col min="11" max="11" width="17.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.77734375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
+    <col min="1" max="1" width="4" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="2" customWidth="1"/>
+    <col min="7" max="10" width="11.42578125" style="2"/>
+    <col min="11" max="11" width="17.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -7286,7 +7891,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>28</v>
       </c>
@@ -7303,7 +7908,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>29</v>
       </c>
@@ -7320,7 +7925,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>30</v>
       </c>
@@ -7337,7 +7942,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>31</v>
       </c>
@@ -7354,7 +7959,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>32</v>
       </c>
@@ -7371,7 +7976,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13"/>
       <c r="C13"/>
       <c r="H13"/>
@@ -7379,7 +7984,7 @@
       <c r="J13"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>23</v>
       </c>
@@ -7396,7 +8001,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="str">
         <f>HLOOKUP(B8,B8:F$12,1,FALSE)</f>
         <v>Juan</v>
@@ -7418,7 +8023,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="str">
         <f>HLOOKUP(B9,B9:F$12,1,FALSE)</f>
         <v>Jesús</v>
@@ -7440,7 +8045,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="str">
         <f>HLOOKUP(B10,B10:F$12,1,FALSE)</f>
         <v>Rosalía</v>
@@ -7462,7 +8067,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="str">
         <f>HLOOKUP(B11,B11:F$12,1,FALSE)</f>
         <v>Leo</v>
@@ -7484,7 +8089,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="str">
         <f>HLOOKUP(B12,B12:F$12,1,FALSE)</f>
         <v>Cristiano</v>
@@ -7506,35 +8111,35 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
       <c r="F21"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
       <c r="F23"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
       <c r="F24"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -7553,17 +8158,17 @@
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="B7:K24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="11.5546875" style="14"/>
-    <col min="8" max="8" width="13.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.5546875" style="14"/>
+    <col min="1" max="7" width="11.42578125" style="13"/>
+    <col min="8" max="8" width="13.28515625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="13" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="13" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>42</v>
       </c>
@@ -7580,20 +8185,20 @@
       <c r="I7"/>
       <c r="J7"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>30</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <v>350</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <v>250</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>300</v>
       </c>
       <c r="H8" t="s">
@@ -7609,121 +8214,121 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>100</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>59</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>63</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>22</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>930</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <v>494</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="15">
         <v>403</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="15">
         <v>1222</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <v>800</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <v>85</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <v>90</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>900</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
     </row>
-    <row r="17" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18"/>
     </row>
-    <row r="19" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
     </row>
-    <row r="20" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20"/>
     </row>
-    <row r="21" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21"/>
     </row>
-    <row r="22" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
     </row>
-    <row r="23" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23"/>
     </row>
-    <row r="24" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24"/>
@@ -7733,4 +8338,367 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C45C9B-BD5D-49D8-9E21-3290B817EA68}">
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051596D5-40C4-4355-B2BC-457BD4A39608}">
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="B5:M33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="26">
+        <f>DATE(2024,12,4)</f>
+        <v>45630</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="28">
+        <f>MONTH(D5)</f>
+        <v>12</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="28">
+        <f>EDATE(D5,8)</f>
+        <v>45873</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="21">
+        <f>DATE(2000,12,4)</f>
+        <v>36864</v>
+      </c>
+      <c r="M10" s="21">
+        <f ca="1">TODAY()</f>
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="16">
+        <v>2</v>
+      </c>
+      <c r="H11" s="16">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="21">
+        <f>DATE(2000,12,31)</f>
+        <v>36891</v>
+      </c>
+      <c r="M11" s="21">
+        <f>DATE(2002,1,20)</f>
+        <v>37276</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2">
+        <v>5</v>
+      </c>
+      <c r="D12" s="17">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="16">
+        <v>9</v>
+      </c>
+      <c r="H12" s="16">
+        <v>10</v>
+      </c>
+      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="22">
+        <f>_xlfn.DAYS(K11,K10)</f>
+        <v>27</v>
+      </c>
+      <c r="M12" s="21">
+        <f ca="1">_xlfn.DAYS(M10,M11)</f>
+        <v>8354</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" s="16">
+        <v>16</v>
+      </c>
+      <c r="H13" s="16">
+        <v>17</v>
+      </c>
+      <c r="J13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="18">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2">
+        <v>29</v>
+      </c>
+      <c r="G14" s="16">
+        <v>30</v>
+      </c>
+      <c r="H14" s="16">
+        <v>31</v>
+      </c>
+      <c r="J14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="16">
+        <v>2</v>
+      </c>
+      <c r="H20" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>4</v>
+      </c>
+      <c r="C21" s="2">
+        <v>5</v>
+      </c>
+      <c r="D21" s="17">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2">
+        <v>7</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="16">
+        <v>9</v>
+      </c>
+      <c r="H21" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2">
+        <v>14</v>
+      </c>
+      <c r="F22" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" s="16">
+        <v>16</v>
+      </c>
+      <c r="H22" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="18">
+        <v>25</v>
+      </c>
+      <c r="C23" s="2">
+        <v>26</v>
+      </c>
+      <c r="D23" s="2">
+        <v>27</v>
+      </c>
+      <c r="E23" s="2">
+        <v>28</v>
+      </c>
+      <c r="F23" s="2">
+        <v>29</v>
+      </c>
+      <c r="G23" s="16">
+        <v>30</v>
+      </c>
+      <c r="H23" s="16">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="20">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C30" s="20">
+        <v>0.62847222222222221</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="20">
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="20">
+        <v>0.30208333333333331</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="20">
+        <v>0.3298611111111111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B18:H18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Apuntes.xlsx
+++ b/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Apuntes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAW\asignaturas\BI\EXCEL\Evaluacion2\noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB75D64E-0FBC-47E7-B7CD-05AA81F6FD27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994D55CB-0419-420B-82DE-703FF85C801A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12090" activeTab="5" xr2:uid="{C1A1F3CA-DEB3-4116-98D3-6D6318BE211A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12090" activeTab="6" xr2:uid="{C1A1F3CA-DEB3-4116-98D3-6D6318BE211A}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="2" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="gráficos" sheetId="6" r:id="rId4"/>
     <sheet name="BuscarX" sheetId="7" r:id="rId5"/>
     <sheet name="Fechas" sheetId="8" r:id="rId6"/>
+    <sheet name="Seguiridad" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlcn.WorksheetConnection_gráficosC7F101" hidden="1">gráficos!$C$7:$F$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -397,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -457,12 +458,6 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -475,6 +470,16 @@
     <xf numFmtId="14" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6669,7 +6674,14 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6743,7 +6755,14 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6812,7 +6831,14 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -6842,6 +6868,239 @@
               </a:solidFill>
             </a:rPr>
             <a:t>Fechas</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>303610</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>303609</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectángulo 17">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDEBA120-44AD-4ADA-870C-9D72F36A1479}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7923610" y="1809750"/>
+          <a:ext cx="1523999" cy="342899"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>9 DE DICIEMBRE</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>491729</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>178592</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>58341</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>140492</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectángulo 18">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8969A8A-3644-4A41-9D5E-87397EC021D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8111729" y="2274092"/>
+          <a:ext cx="1090612" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Proteccion</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>661988</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>125016</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>602456</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>86916</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rectángulo 19">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B647E12E-D545-46AD-B029-1C7A0697B4DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8281988" y="2792016"/>
+          <a:ext cx="702468" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Ejemplos</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -7138,6 +7397,98 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>13422</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F9339E-78EB-4834-A0FF-6F5D3DD8BC47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="733425" y="2324101"/>
+          <a:ext cx="2327997" cy="2533650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>733424</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>63527</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65468BA8-4C1E-47BF-98D8-302A945F9DDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect l="56093" r="23883"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="733424" y="752475"/>
+          <a:ext cx="2333625" cy="1406552"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="FP" refreshedDate="45628.388513310187" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{477C061B-19F7-4DB1-9ED9-1E87A5200B78}">
   <cacheSource type="external" connectionId="1"/>
@@ -7215,7 +7566,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF192066-03ED-4ACB-997B-4D39A9E47C78}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF192066-03ED-4ACB-997B-4D39A9E47C78}" name="TablaDinámica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="H8:K9" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="4">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -7580,13 +7931,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8DA10F8-0EF7-48EA-90FF-9F055AACE164}">
   <sheetPr>
-    <tabColor theme="9" tint="-0.249977111117893"/>
+    <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7667,12 +8019,12 @@
         <f t="shared" ref="F9:F15" si="1">VLOOKUP(C9,H$10:K$13,4,FALSE)</f>
         <v>EN</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
@@ -8368,38 +8720,38 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="24">
         <f>DATE(2024,12,4)</f>
         <v>45630</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="26">
         <f>MONTH(D5)</f>
         <v>12</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="26">
         <f>EDATE(D5,8)</f>
         <v>45873</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
@@ -8432,7 +8784,7 @@
       </c>
       <c r="M10" s="21">
         <f ca="1">TODAY()</f>
-        <v>45630</v>
+        <v>45635</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
@@ -8492,7 +8844,7 @@
       </c>
       <c r="M12" s="21">
         <f ca="1">_xlfn.DAYS(M10,M11)</f>
-        <v>8354</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
@@ -8548,15 +8900,15 @@
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="19" t="s">
@@ -8701,4 +9053,25 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22E9F95-4BC9-434F-ACEA-242C11851E6C}">
+  <sheetPr>
+    <tabColor theme="9" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="30"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>